--- a/assessment_forms/033_exponential_functions_assessment--assessment_forms.xlsx
+++ b/assessment_forms/033_exponential_functions_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option c</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option c</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option c</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option c</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option c</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option c</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option c</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option c</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option c</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option c</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option c</t>
         </is>
       </c>
     </row>
